--- a/data/processed/harmonization/Major_and_trace_elements_total__Total_cadmium/dois_filtering.xlsx
+++ b/data/processed/harmonization/Major_and_trace_elements_total__Total_cadmium/dois_filtering.xlsx
@@ -546,7 +546,7 @@
         <v>24</v>
       </c>
       <c r="D2">
-        <v>286</v>
+        <v>292</v>
       </c>
       <c r="E2" t="s">
         <v>37</v>
